--- a/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67564</t>
+          <t>67787</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>101808</t>
+          <t>103343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106452</t>
+          <t>106244</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>148929</t>
+          <t>147235</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>184507</t>
+          <t>185791</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>237953</t>
+          <t>241390</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>929915</t>
+          <t>928380</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>964159</t>
+          <t>963936</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1166184</t>
+          <t>1167878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1208661</t>
+          <t>1208869</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,68%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,92%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2108882</t>
+          <t>2105445</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2162328</t>
+          <t>2161044</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>92,08%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48845</t>
+          <t>47831</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>79706</t>
+          <t>78637</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47284</t>
+          <t>48871</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78884</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104330</t>
+          <t>104850</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>146647</t>
+          <t>147697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1613707</t>
+          <t>1614776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1644568</t>
+          <t>1645582</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1508789</t>
+          <t>1507498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1540389</t>
+          <t>1538802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3134439</t>
+          <t>3133389</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3176756</t>
+          <t>3176236</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8485</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25786</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14734</t>
+          <t>14559</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34626</t>
+          <t>34171</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>26091</t>
+          <t>27439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52555</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>525622</t>
+          <t>524542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>542923</t>
+          <t>543136</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>441786</t>
+          <t>442241</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461678</t>
+          <t>461853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>975265</t>
+          <t>974864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1001729</t>
+          <t>1000381</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139518</t>
+          <t>140911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>191126</t>
+          <t>188514</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>183046</t>
+          <t>185394</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>240842</t>
+          <t>242778</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>338131</t>
+          <t>341330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>415727</t>
+          <t>414212</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3085417</t>
+          <t>3088029</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3137025</t>
+          <t>3135632</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3138355</t>
+          <t>3136419</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3196151</t>
+          <t>3193803</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6240014</t>
+          <t>6241529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6317610</t>
+          <t>6314411</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>107221</t>
+          <t>104492</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>155793</t>
+          <t>150758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>153040</t>
+          <t>149752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>202078</t>
+          <t>205514</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>267263</t>
+          <t>270927</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337761</t>
+          <t>337143</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,58%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>818850</t>
+          <t>823885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>867422</t>
+          <t>870151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,02%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1135719</t>
+          <t>1132283</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1184757</t>
+          <t>1188045</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1974679</t>
+          <t>1975297</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2045177</t>
+          <t>2041513</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,44%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87527</t>
+          <t>83202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>127640</t>
+          <t>126043</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105476</t>
+          <t>105581</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150353</t>
+          <t>150908</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200789</t>
+          <t>200411</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259555</t>
+          <t>259832</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1836317</t>
+          <t>1837914</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1876430</t>
+          <t>1880755</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1607450</t>
+          <t>1606895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1652327</t>
+          <t>1652222</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3462205</t>
+          <t>3461928</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3520971</t>
+          <t>3521349</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11075</t>
+          <t>10700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>30821</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15379</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37034</t>
+          <t>34697</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29781</t>
+          <t>28991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58752</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,1%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>451942</t>
+          <t>450360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470106</t>
+          <t>470481</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>421597</t>
+          <t>423934</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>443252</t>
+          <t>444358</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>881061</t>
+          <t>882465</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>910032</t>
+          <t>910822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>218668</t>
+          <t>219790</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>289557</t>
+          <t>283323</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>287923</t>
+          <t>288167</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>361708</t>
+          <t>360029</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>523709</t>
+          <t>527182</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>616876</t>
+          <t>622719</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3130225</t>
+          <t>3136459</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3201114</t>
+          <t>3199992</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,53%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,61%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3192522</t>
+          <t>3194201</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3266307</t>
+          <t>3266063</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6357136</t>
+          <t>6351293</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6450303</t>
+          <t>6446830</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48936</t>
+          <t>47647</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79865</t>
+          <t>79287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>107763</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155041</t>
+          <t>153342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>167213</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>218566</t>
+          <t>221163</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,65%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>674482</t>
+          <t>675060</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>705411</t>
+          <t>706700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>839619</t>
+          <t>841318</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>886884</t>
+          <t>886897</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1530441</t>
+          <t>1527844</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1583256</t>
+          <t>1581794</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86897</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>129845</t>
+          <t>125950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75488</t>
+          <t>75583</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>115378</t>
+          <t>114744</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>169775</t>
+          <t>171670</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>227773</t>
+          <t>226853</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1946540</t>
+          <t>1950435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1989488</t>
+          <t>1990535</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1872922</t>
+          <t>1873556</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1912812</t>
+          <t>1912717</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3836912</t>
+          <t>3837832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3894910</t>
+          <t>3893015</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11597</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>32072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13669</t>
+          <t>13631</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32315</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29915</t>
+          <t>30628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>57610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,26%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>516885</t>
+          <t>514814</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>535289</t>
+          <t>534964</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516825</t>
+          <t>516670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535471</t>
+          <t>535509</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1040407</t>
+          <t>1038417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1066112</t>
+          <t>1065399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>162824</t>
+          <t>160574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214731</t>
+          <t>214788</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>212349</t>
+          <t>213301</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275438</t>
+          <t>275470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>388292</t>
+          <t>391077</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>473126</t>
+          <t>470440</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,81%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3162887</t>
+          <t>3162830</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3214794</t>
+          <t>3217044</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3256662</t>
+          <t>3256630</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3319751</t>
+          <t>3318799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6436592</t>
+          <t>6439278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6521426</t>
+          <t>6518641</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>101623</t>
+          <t>99502</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135300</t>
+          <t>134800</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>160243</t>
+          <t>161565</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>193838</t>
+          <t>195646</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>269413</t>
+          <t>270145</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>320293</t>
+          <t>316380</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>24,9%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379638</t>
+          <t>380138</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>413315</t>
+          <t>415436</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,26%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>561670</t>
+          <t>559862</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>595265</t>
+          <t>593943</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>950153</t>
+          <t>954066</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1001033</t>
+          <t>1000301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,74%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>142074</t>
+          <t>143677</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>242223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174852</t>
+          <t>174700</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>899709</t>
+          <t>838316</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>37,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>366860</t>
+          <t>363774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1219303</t>
+          <t>1215187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2051471</t>
+          <t>2048104</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2148253</t>
+          <t>2146650</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1338114</t>
+          <t>1399507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2062971</t>
+          <t>2063123</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>62,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3308847</t>
+          <t>3312963</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4161290</t>
+          <t>4164376</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,07%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,97%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>32716</t>
+          <t>31359</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>62444</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26034</t>
+          <t>26044</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>44884</t>
+          <t>45693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62852</t>
+          <t>64486</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>98330</t>
+          <t>99076</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>582814</t>
+          <t>584179</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>613907</t>
+          <t>615264</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>615579</t>
+          <t>614770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634429</t>
+          <t>634419</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1208756</t>
+          <t>1208010</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1244234</t>
+          <t>1242600</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>284731</t>
+          <t>285403</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>408401</t>
+          <t>410474</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>388086</t>
+          <t>391228</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1158747</t>
+          <t>1158887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>735125</t>
+          <t>736870</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1626636</t>
+          <t>1613918</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3043488</t>
+          <t>3041415</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3167158</t>
+          <t>3166486</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2495047</t>
+          <t>2494907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3265708</t>
+          <t>3262566</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5479047</t>
+          <t>5491765</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6370558</t>
+          <t>6368813</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>67787</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>103343</t>
+          <t>104935</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>106244</t>
+          <t>106585</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>147235</t>
+          <t>149218</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>185791</t>
+          <t>186603</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>241390</t>
+          <t>241330</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>928380</t>
+          <t>926788</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>963936</t>
+          <t>962565</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1167878</t>
+          <t>1165895</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1208869</t>
+          <t>1208528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2105445</t>
+          <t>2105505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2161044</t>
+          <t>2160232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,71%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47831</t>
+          <t>50116</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>78637</t>
+          <t>79769</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>48871</t>
+          <t>47056</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>80175</t>
+          <t>79569</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>104850</t>
+          <t>104666</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147697</t>
+          <t>150493</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,59%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1614776</t>
+          <t>1613644</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1645582</t>
+          <t>1643297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1507498</t>
+          <t>1508104</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1538802</t>
+          <t>1540617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3133389</t>
+          <t>3130593</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3176236</t>
+          <t>3176420</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,81%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8272</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>26275</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14559</t>
+          <t>14590</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34171</t>
+          <t>35571</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27439</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>53750</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>524542</t>
+          <t>525133</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>543136</t>
+          <t>542736</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442241</t>
+          <t>440841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>461853</t>
+          <t>461822</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>974864</t>
+          <t>974070</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1000381</t>
+          <t>1000349</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140911</t>
+          <t>138475</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188514</t>
+          <t>189999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>185394</t>
+          <t>182438</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>242778</t>
+          <t>241226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>341330</t>
+          <t>338008</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414212</t>
+          <t>411953</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3088029</t>
+          <t>3086544</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3135632</t>
+          <t>3138068</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3136419</t>
+          <t>3137971</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3193803</t>
+          <t>3196759</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6241529</t>
+          <t>6243788</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6314411</t>
+          <t>6317733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,78%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,92%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>104492</t>
+          <t>104507</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>150758</t>
+          <t>150796</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>149752</t>
+          <t>150597</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>205514</t>
+          <t>203421</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270927</t>
+          <t>267985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>337143</t>
+          <t>335120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>823885</t>
+          <t>823847</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>870151</t>
+          <t>870136</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1132283</t>
+          <t>1134376</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1188045</t>
+          <t>1187200</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1975297</t>
+          <t>1977320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2041513</t>
+          <t>2044455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83202</t>
+          <t>85497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>126043</t>
+          <t>125582</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105581</t>
+          <t>105097</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150908</t>
+          <t>151554</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>200411</t>
+          <t>200211</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>259832</t>
+          <t>261540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2769,7 +2769,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1837914</t>
+          <t>1838375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1880755</t>
+          <t>1878460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1606895</t>
+          <t>1606249</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1652222</t>
+          <t>1652706</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3461928</t>
+          <t>3460220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3521349</t>
+          <t>3521549</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,7 +2877,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10700</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30821</t>
+          <t>29869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>14273</t>
+          <t>14902</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34697</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28991</t>
+          <t>30042</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57348</t>
+          <t>59123</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>450360</t>
+          <t>451312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>470481</t>
+          <t>470434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,59%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>423934</t>
+          <t>423110</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>444358</t>
+          <t>443729</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>882465</t>
+          <t>880690</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>910822</t>
+          <t>909771</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,8%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>219790</t>
+          <t>220195</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>283323</t>
+          <t>284922</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>288167</t>
+          <t>287995</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>360029</t>
+          <t>358518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>527182</t>
+          <t>526227</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>622719</t>
+          <t>617423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3136459</t>
+          <t>3134860</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3199992</t>
+          <t>3199587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,72%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3194201</t>
+          <t>3195712</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3266063</t>
+          <t>3266235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6351293</t>
+          <t>6356589</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6446830</t>
+          <t>6447785</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>47647</t>
+          <t>49871</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>79287</t>
+          <t>80078</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>107763</t>
+          <t>107289</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153342</t>
+          <t>152034</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>167213</t>
+          <t>162438</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>221163</t>
+          <t>220204</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675060</t>
+          <t>674269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>706700</t>
+          <t>704476</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>841318</t>
+          <t>842626</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>886897</t>
+          <t>887371</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,17%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1527844</t>
+          <t>1528803</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1581794</t>
+          <t>1586569</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,71%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85850</t>
+          <t>84407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125950</t>
+          <t>124260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75583</t>
+          <t>74170</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114744</t>
+          <t>113456</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171670</t>
+          <t>169554</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>226853</t>
+          <t>224875</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1950435</t>
+          <t>1952125</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1990535</t>
+          <t>1991978</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1873556</t>
+          <t>1874844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1912717</t>
+          <t>1914130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3837832</t>
+          <t>3839810</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3893015</t>
+          <t>3895131</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11922</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>32072</t>
+          <t>29769</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13631</t>
+          <t>13618</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>32404</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30628</t>
+          <t>28935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57610</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>514814</t>
+          <t>517117</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>534964</t>
+          <t>535483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516670</t>
+          <t>516736</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>535509</t>
+          <t>535522</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1038417</t>
+          <t>1039333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1065399</t>
+          <t>1067092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>160574</t>
+          <t>161544</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>214788</t>
+          <t>216733</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>213301</t>
+          <t>214667</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>275470</t>
+          <t>276003</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>391077</t>
+          <t>390782</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>470440</t>
+          <t>470528</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3162830</t>
+          <t>3160885</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3217044</t>
+          <t>3216074</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3256630</t>
+          <t>3256097</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3318799</t>
+          <t>3317433</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6439278</t>
+          <t>6439190</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6518641</t>
+          <t>6518936</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>116353</t>
+          <t>123049</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>99502</t>
+          <t>107182</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>134800</t>
+          <t>145260</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>177802</t>
+          <t>194599</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>161565</t>
+          <t>177429</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>195646</t>
+          <t>215470</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,53%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>26,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>294155</t>
+          <t>317648</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>270145</t>
+          <t>291829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>316380</t>
+          <t>345190</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>398585</t>
+          <t>455480</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>380138</t>
+          <t>433269</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>415436</t>
+          <t>471347</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>78,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>577706</t>
+          <t>627439</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>559862</t>
+          <t>606568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>593943</t>
+          <t>644609</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,1%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>976291</t>
+          <t>1082919</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>954066</t>
+          <t>1055377</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1000301</t>
+          <t>1108738</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>76,85%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,74%</t>
+          <t>79,16%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>514938</t>
+          <t>578529</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>755508</t>
+          <t>822038</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1400567</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>200233</t>
+          <t>211159</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>143677</t>
+          <t>183890</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>242223</t>
+          <t>239235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>371494</t>
+          <t>192035</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174700</t>
+          <t>170051</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>838316</t>
+          <t>218551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,46%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>571727</t>
+          <t>403194</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>363774</t>
+          <t>366408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1215187</t>
+          <t>443083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2090094</t>
+          <t>2019407</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2048104</t>
+          <t>1991331</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2146650</t>
+          <t>2046676</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>91,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1866329</t>
+          <t>1979357</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1399507</t>
+          <t>1952841</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2063123</t>
+          <t>2001341</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,54%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3956423</t>
+          <t>3998765</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3312963</t>
+          <t>3958876</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4164376</t>
+          <t>4035551</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2290327</t>
+          <t>2230566</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2237823</t>
+          <t>2171392</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4528150</t>
+          <t>4401959</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>49468</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31359</t>
+          <t>35592</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>62444</t>
+          <t>68172</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>34223</t>
+          <t>40112</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>31398</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45693</t>
+          <t>52670</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>79628</t>
+          <t>89580</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64486</t>
+          <t>72034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>99076</t>
+          <t>110866</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>601218</t>
+          <t>662119</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>584179</t>
+          <t>643415</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>615264</t>
+          <t>675995</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>626240</t>
+          <t>694765</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>614770</t>
+          <t>682207</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>634419</t>
+          <t>703479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1227458</t>
+          <t>1356884</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1208010</t>
+          <t>1335598</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1242600</t>
+          <t>1374430</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>95,02%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1307086</t>
+          <t>1446464</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>361991</t>
+          <t>383676</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>285403</t>
+          <t>345689</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>410474</t>
+          <t>422247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>583519</t>
+          <t>426747</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>391228</t>
+          <t>396069</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1158887</t>
+          <t>463170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>945510</t>
+          <t>810422</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>736870</t>
+          <t>764862</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1613918</t>
+          <t>860632</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3089898</t>
+          <t>3137007</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3041415</t>
+          <t>3098436</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3166486</t>
+          <t>3174994</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>89,51%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>88,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3070275</t>
+          <t>3301560</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2494907</t>
+          <t>3265137</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3262566</t>
+          <t>3332238</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6160173</t>
+          <t>6438568</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5491765</t>
+          <t>6388358</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6368813</t>
+          <t>6484128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>77,29%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,45%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3451889</t>
+          <t>3520683</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3653794</t>
+          <t>3728307</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7105683</t>
+          <t>7248990</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P2A_fisi_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad física en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
